--- a/data/trans_bre/IP26C_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP26C_R-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 9,52</t>
+          <t>-4,77; 10,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,72; 3,56</t>
+          <t>-9,07; 3,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 7,3</t>
+          <t>-5,79; 7,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,74; 1,62</t>
+          <t>-11,71; 1,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-33,9; 131,76</t>
+          <t>-35,13; 153,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-74,03; 71,99</t>
+          <t>-71,78; 59,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-52,65; 148,28</t>
+          <t>-50,83; 143,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-68,83; 18,58</t>
+          <t>-68,19; 21,1</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 10,04</t>
+          <t>-3,46; 10,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 10,24</t>
+          <t>-4,18; 11,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 8,21</t>
+          <t>-5,59; 7,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 7,13</t>
+          <t>-7,44; 7,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-42,25; 332,71</t>
+          <t>-40,36; 364,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-39,53; 143,39</t>
+          <t>-30,02; 170,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-47,94; 163,39</t>
+          <t>-47,0; 150,06</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-53,52; 124,28</t>
+          <t>-58,45; 121,69</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,78; 8,18</t>
+          <t>-8,74; 8,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,49; 7,49</t>
+          <t>-6,55; 7,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,17; 4,89</t>
+          <t>-11,74; 5,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-18,62; 1,8</t>
+          <t>-19,8; 1,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-51,97; 76,99</t>
+          <t>-54,01; 82,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-49,1; 124,55</t>
+          <t>-51,04; 113,01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-69,78; 91,58</t>
+          <t>-72,79; 69,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-79,5; 21,52</t>
+          <t>-86,34; 13,84</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 2,56</t>
+          <t>-8,29; 1,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 2,63</t>
+          <t>-6,88; 2,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 5,26</t>
+          <t>-3,85; 5,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 5,48</t>
+          <t>-3,53; 5,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-51,66; 26,08</t>
+          <t>-54,39; 21,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-54,46; 34,26</t>
+          <t>-54,74; 29,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-35,04; 68,3</t>
+          <t>-32,49; 75,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-41,61; 113,25</t>
+          <t>-39,83; 128,63</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,94; 14,87</t>
+          <t>1,66; 13,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 4,86</t>
+          <t>-7,87; 5,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 4,52</t>
+          <t>-6,73; 4,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 9,79</t>
+          <t>-3,3; 10,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,97; 507,52</t>
+          <t>14,66; 501,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-49,42; 51,07</t>
+          <t>-48,99; 56,9</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-54,6; 77,21</t>
+          <t>-59,21; 78,66</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-28,34; 141,3</t>
+          <t>-29,25; 149,99</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,8; 17,36</t>
+          <t>2,21; 17,9</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-10,01; 13,23</t>
+          <t>-8,78; 14,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 12,88</t>
+          <t>-4,54; 13,59</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-24,58; -5,29</t>
+          <t>-24,78; -4,89</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>14,45; 552,54</t>
+          <t>10,71; 546,93</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-45,89; 120,56</t>
+          <t>-42,61; 112,58</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-49,0; 467,64</t>
+          <t>-45,01; 455,32</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-90,24; -34,69</t>
+          <t>-91,57; -34,39</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 5,01</t>
+          <t>-0,67; 4,96</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 1,63</t>
+          <t>-3,7; 1,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 2,97</t>
+          <t>-2,13; 2,95</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 0,71</t>
+          <t>-5,1; 0,71</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 62,85</t>
+          <t>-6,14; 59,94</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-29,4; 17,1</t>
+          <t>-29,42; 18,23</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-21,28; 37,98</t>
+          <t>-21,87; 37,21</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-39,77; 7,8</t>
+          <t>-40,73; 7,12</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP26C_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP26C_R-Clase-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según que han tenido una quemadura en el último año</t>
+          <t>Menores según si han tenido una quemadura solar, con o sin ampollas, en el último año</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 10,08</t>
+          <t>-4,39; 9,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,07; 3,18</t>
+          <t>-9,71; 3,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 7,57</t>
+          <t>-5,88; 7,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,71; 1,47</t>
+          <t>-12,15; 2,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-35,13; 153,87</t>
+          <t>-34,32; 140,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-71,78; 59,7</t>
+          <t>-74,47; 67,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-50,83; 143,54</t>
+          <t>-51,58; 142,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-68,19; 21,1</t>
+          <t>-70,92; 23,01</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 10,34</t>
+          <t>-3,06; 10,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 11,06</t>
+          <t>-4,36; 10,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 7,31</t>
+          <t>-5,48; 7,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 7,28</t>
+          <t>-6,96; 6,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-40,36; 364,43</t>
+          <t>-33,74; 300,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-30,02; 170,44</t>
+          <t>-33,98; 146,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-47,0; 150,06</t>
+          <t>-47,89; 145,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-58,45; 121,69</t>
+          <t>-53,85; 128,87</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,74; 8,36</t>
+          <t>-8,98; 9,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 7,74</t>
+          <t>-7,21; 7,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,74; 5,07</t>
+          <t>-11,77; 5,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-19,8; 1,09</t>
+          <t>-19,71; 1,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-54,01; 82,32</t>
+          <t>-53,27; 90,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-51,04; 113,01</t>
+          <t>-55,81; 119,41</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-72,79; 69,27</t>
+          <t>-71,05; 82,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-86,34; 13,84</t>
+          <t>-83,53; 29,11</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,29; 1,91</t>
+          <t>-7,25; 2,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,88; 2,19</t>
+          <t>-6,33; 2,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 5,48</t>
+          <t>-3,98; 5,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 5,85</t>
+          <t>-3,2; 6,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-54,39; 21,67</t>
+          <t>-50,35; 27,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-54,74; 29,37</t>
+          <t>-51,99; 30,84</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-32,49; 75,94</t>
+          <t>-32,51; 77,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-39,83; 128,63</t>
+          <t>-38,12; 122,42</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,66; 13,91</t>
+          <t>1,78; 14,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 5,14</t>
+          <t>-6,75; 5,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 4,11</t>
+          <t>-6,24; 4,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 10,81</t>
+          <t>-2,77; 10,7</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,66; 501,54</t>
+          <t>17,18; 467,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-48,99; 56,9</t>
+          <t>-45,71; 69,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-59,21; 78,66</t>
+          <t>-56,82; 83,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-29,25; 149,99</t>
+          <t>-25,98; 153,53</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,21; 17,9</t>
+          <t>2,34; 18,99</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,78; 14,0</t>
+          <t>-9,41; 13,65</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 13,59</t>
+          <t>-3,21; 13,54</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-24,78; -4,89</t>
+          <t>-24,36; -4,87</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10,71; 546,93</t>
+          <t>1,35; 563,07</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-42,61; 112,58</t>
+          <t>-45,17; 117,95</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-45,01; 455,32</t>
+          <t>-41,55; 539,16</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-91,57; -34,39</t>
+          <t>-90,63; -30,01</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 4,96</t>
+          <t>-0,49; 4,76</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 1,72</t>
+          <t>-3,53; 1,84</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 2,95</t>
+          <t>-2,27; 2,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 0,71</t>
+          <t>-5,06; 0,74</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 59,94</t>
+          <t>-4,59; 58,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-29,42; 18,23</t>
+          <t>-28,55; 18,6</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-21,87; 37,21</t>
+          <t>-21,81; 38,06</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-40,73; 7,12</t>
+          <t>-40,35; 7,96</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP26C_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP26C_R-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-5,17</t>
+          <t>-5,42</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-38,17%</t>
+          <t>-38,45%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 9,67</t>
+          <t>-4,3; 9,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,71; 3,6</t>
+          <t>-9,72; 3,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 7,67</t>
+          <t>-6,19; 7,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,15; 2,01</t>
+          <t>-12,29; 1,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-34,32; 140,31</t>
+          <t>-33,9; 131,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-74,47; 67,85</t>
+          <t>-74,03; 71,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-51,58; 142,36</t>
+          <t>-52,65; 148,28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-70,92; 23,01</t>
+          <t>-68,97; 20,12</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>-0,4</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>-3,92%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 10,24</t>
+          <t>-3,17; 10,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 10,78</t>
+          <t>-5,23; 10,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 7,76</t>
+          <t>-4,93; 8,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 6,9</t>
+          <t>-7,83; 7,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-33,74; 300,06</t>
+          <t>-42,25; 332,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-33,98; 146,53</t>
+          <t>-39,53; 143,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-47,89; 145,17</t>
+          <t>-47,94; 163,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-53,85; 128,87</t>
+          <t>-57,02; 112,38</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-8,44</t>
+          <t>-9,63</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-49,44%</t>
+          <t>-52,41%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 9,12</t>
+          <t>-8,78; 8,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,21; 7,45</t>
+          <t>-6,49; 7,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,77; 5,56</t>
+          <t>-11,17; 4,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-19,71; 1,46</t>
+          <t>-20,66; 1,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-53,27; 90,21</t>
+          <t>-51,97; 76,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-55,81; 119,41</t>
+          <t>-49,1; 124,55</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-71,05; 82,16</t>
+          <t>-69,78; 91,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-83,53; 29,11</t>
+          <t>-81,34; 18,02</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,29</t>
+          <t>2,57</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>36,5%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 2,58</t>
+          <t>-7,6; 2,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 2,53</t>
+          <t>-6,67; 2,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 5,77</t>
+          <t>-4,31; 5,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 6,19</t>
+          <t>-2,39; 6,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-50,35; 27,34</t>
+          <t>-51,66; 26,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-51,99; 30,84</t>
+          <t>-54,46; 34,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-32,51; 77,29</t>
+          <t>-35,04; 68,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-38,12; 122,42</t>
+          <t>-27,31; 144,23</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,48</t>
+          <t>3,51</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>33,23%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,78; 14,09</t>
+          <t>1,94; 14,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 5,9</t>
+          <t>-7,74; 4,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 4,31</t>
+          <t>-5,84; 4,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 10,7</t>
+          <t>-4,03; 9,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,18; 467,96</t>
+          <t>18,97; 507,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-45,71; 69,24</t>
+          <t>-49,42; 51,07</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-56,82; 83,35</t>
+          <t>-54,6; 77,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-25,98; 153,53</t>
+          <t>-29,97; 139,89</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-13,87</t>
+          <t>-13,37</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-73,74%</t>
+          <t>-74,58%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,34; 18,99</t>
+          <t>1,8; 17,36</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-9,41; 13,65</t>
+          <t>-10,01; 13,23</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 13,54</t>
+          <t>-4,52; 12,88</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-24,36; -4,87</t>
+          <t>-23,62; -5,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,35; 563,07</t>
+          <t>14,45; 552,54</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-45,17; 117,95</t>
+          <t>-45,89; 120,56</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-41,55; 539,16</t>
+          <t>-49,0; 467,64</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-90,63; -30,01</t>
+          <t>-90,86; -33,64</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-2,06</t>
+          <t>-1,79</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-18,66%</t>
+          <t>-15,61%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 4,76</t>
+          <t>-0,54; 5,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 1,84</t>
+          <t>-3,67; 1,63</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 2,93</t>
+          <t>-2,16; 2,97</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 0,74</t>
+          <t>-4,7; 1,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 58,43</t>
+          <t>-5,29; 62,85</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-28,55; 18,6</t>
+          <t>-29,4; 17,1</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-21,81; 38,06</t>
+          <t>-21,28; 37,98</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-40,35; 7,96</t>
+          <t>-35,81; 12,05</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP26C_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP26C_R-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>2,49</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-3,36</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,74</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-5,42</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>23,93%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-34,47%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8,63%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-38,45%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>2.490072707391155</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-3.363994543151584</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.7426614537782622</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-5.41686824660662</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.2392508443360359</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.3446542805453855</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.08626377887914752</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.3845134199331051</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-4,3; 9,52</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-9,72; 3,56</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-6,19; 7,3</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-12,29; 1,53</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-33,9; 131,76</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-74,03; 71,99</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-52,65; 148,28</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-68,97; 20,12</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-4.295124313519153</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-9.720905711900929</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-6.186858151007198</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-12.29151490583858</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.3390107712114534</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.740322817596669</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.526487715740256</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.6896815493683445</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>9.522590314810474</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>3.559147905858859</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>7.299785725890934</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>1.531426317240121</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>1.317569212146306</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.719913819781099</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>1.482793874959216</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.2012442624625521</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>3,36</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>3,0</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,91</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-0,4</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>54,32%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>27,9%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>10,81%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-3,92%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-3,17; 10,04</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-5,23; 10,24</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-4,93; 8,21</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-7,83; 7,01</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-42,25; 332,71</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-39,53; 143,39</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-47,94; 163,39</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-57,02; 112,38</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>3.361135399963967</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>3.000532778328977</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.9073137856625973</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-0.3966120121420252</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.5432434023750092</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.2789743104698325</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.1080783537286281</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.0391558172058445</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-0,59</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,16</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-3,03</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-9,63</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-4,29%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,64%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-25,76%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-52,41%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-3.170338330039062</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-5.230964395855053</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-4.928274147158205</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-7.833111482566886</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.4224935847459682</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.3952642703815629</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.4793771000099164</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.5701901561272492</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-8,78; 8,18</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-6,49; 7,49</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-11,17; 4,89</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-20,66; 1,09</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-51,97; 76,99</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-49,1; 124,55</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-69,78; 91,58</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-81,34; 18,02</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>10.04014716830351</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>10.24388673280483</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>8.211002388390513</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>7.014297355658263</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>3.327145508184662</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1.433947667397616</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>1.633874079911494</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>1.123790432121613</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,299 +819,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-2,65</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-2,1</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,74</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2,57</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-21,79%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-20,78%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,64%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>36,5%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-0.5944069699657467</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.1648405785005622</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-3.027706473367422</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-9.625445736517724</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.04292961747560389</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.01640380576542134</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.2576217906543936</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.5241148994592024</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-7,6; 2,56</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-6,67; 2,63</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-4,31; 5,26</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-2,39; 6,93</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-51,66; 26,08</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-54,46; 34,26</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-35,04; 68,3</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-27,31; 144,23</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-8.77880651980033</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-6.489916993112967</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-11.16835230513145</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-20.66164259017194</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.5196799561433094</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.4910226014789403</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.6978286033215818</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.8134235227807443</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>8.184651971951638</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>7.491222983430267</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>4.88754783803022</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>1.094347058436181</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.7699094441561137</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1.245523080230862</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.9157909077123191</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.1802163766160991</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>7,52</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-1,2</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-1,18</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>3,51</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>158,57%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-9,68%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-13,99%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>33,23%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>1,94; 14,87</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-7,74; 4,86</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-5,84; 4,52</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-4,03; 9,89</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>18,97; 507,52</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-49,42; 51,07</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-54,6; 77,21</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-29,97; 139,89</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>-2.651632852896857</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-2.095808754246825</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.7354766588069467</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>2.574984941534094</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.2179107080111343</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.2077886110879108</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.07640394780374361</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.3650491298156294</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>9,68</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>1,19</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>3,98</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-13,37</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>150,04%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>7,02%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>58,34%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-74,58%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-7.596419627526253</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-6.670524084928728</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-4.314901265833896</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-2.387878714920593</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.5165585203607135</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.5445669845546784</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.3503940698868823</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.2730600246178209</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>1,8; 17,36</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-10,01; 13,23</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-4,52; 12,88</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-23,62; -5,0</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>14,45; 552,54</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-45,89; 120,56</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-49,0; 467,64</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-90,86; -33,64</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>2.55660301633364</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>2.631842268391643</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>5.258882450975711</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>6.930734791687867</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.260765868627255</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.3425756718365348</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.6830057795733818</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>1.442345672585384</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1210,97 +1019,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>2,25</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-0,94</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,32</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-1,79</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>23,86%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-8,29%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,51%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-15,61%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>7.517499363596267</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-1.202135983775734</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-1.181378938584922</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>3.507239915727914</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>1.585736994653261</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.09682507266000658</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.1399318481561952</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.3322626573974177</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-0,54; 5,01</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-3,67; 1,63</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-2,16; 2,97</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-4,7; 1,1</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-5,29; 62,85</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-29,4; 17,1</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-21,28; 37,98</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-35,81; 12,05</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>1.939847173783193</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-7.738957955304731</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-5.837016859957962</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-4.029673959380819</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>0.1897317237600949</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.4941999228789369</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.5460198771355569</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.2997370027076148</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>14.86824628339211</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>4.855893667887167</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>4.515315323391471</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>9.888459848486159</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>5.075163522165179</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.5107290252931769</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.7720823471974788</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>1.398940754211952</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>9.680280555144179</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>1.188651564568258</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>3.978157317887758</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>-13.36819419995271</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>1.500397246406046</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>0.07016524034930716</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>0.5833797573389959</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>-0.745807086254147</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>1.795076293420982</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-10.00779241164843</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-4.522873235450644</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>-23.616959544116</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>0.1445284929083127</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.4589065064200125</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>-0.4900478545269813</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>-0.9086233958578085</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>17.35981057699274</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>13.2265870848699</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>12.88388543610625</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>-4.99832042869676</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>5.525441850537506</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>1.205612232535627</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>4.676439888110595</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>-0.3363996764061283</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>2.252013864790295</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-0.9369795962825709</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0.316622652253154</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-1.791607998574569</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>0.2386488901253215</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>-0.08290415904544088</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>0.03514701913312389</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>-0.156114809748558</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-0.5364874631800283</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-3.671450338795178</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-2.164730584881867</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-4.702230084005814</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.05289864627043225</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-0.2940381383970806</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>-0.2127849609008549</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>-0.3580517013626173</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>5.009039713213654</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>1.634685523884372</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>2.974196741635371</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>1.100808623153408</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0.6284591057549371</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>0.1709603104411802</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>0.3797596153983268</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>0.1204904216750639</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1308,16 +1317,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
